--- a/frontend-web/public/templates/SLMS2026_import_dot2_cai_tao.xlsx
+++ b/frontend-web/public/templates/SLMS2026_import_dot2_cai_tao.xlsx
@@ -435,7 +435,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sheet "4. Thiet_Bi_Mua_Moi" (tùy chọn): TB mua + bảo hành; cột Hành động = THEM_MOI (mặc định) hoặc THAY_THE.</v>
+        <v>Sheet "4. Thiet_Bi_Mua_Moi" (tùy chọn): TB mua + bảo hành; Hành động = THEM_MOI hoặc THAY_THE.</v>
       </c>
     </row>
     <row r="7">
@@ -450,7 +450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Xem sheet "0. Ma_Tran_Trường_Hop".</v>
+        <v>Xem sheet "0. Ma_Tran_Trường_Hop" (11 HĐ đợt 2).</v>
       </c>
     </row>
   </sheetData>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F23"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -529,7 +529,7 @@
         <v>—</v>
       </c>
       <c r="F3" t="str">
-        <v>Không cải tạo — sau đợt 1 gửi Host luôn (không có file đợt 2)</v>
+        <v>Không cải tạo — sau đợt 1 gửi Host luôn</v>
       </c>
     </row>
     <row r="4">
@@ -589,42 +589,247 @@
         <v>Có</v>
       </c>
       <c r="F6" t="str">
-        <v>Thuê nguyên căn đợt 1 — đợt 2 chia 5 phòng khai thác + mua TB từng phòng</v>
+        <v>Thuê nguyên căn đợt 1 — đợt 2 chia 5 phòng + mua TB từng phòng</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Có</v>
+      </c>
+      <c r="C7" t="str">
+        <v>THEO_PHONG (8 phòng)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Có</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Nhà trọ 8 phòng — cải tạo kết cấu + TB từng phòng</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Quy tắc:</v>
+        <v>HD-WH-RENO-SPLIT3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Không</v>
+      </c>
+      <c r="C8" t="str">
+        <v>THEO_PHONG (3 phòng)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Có</v>
+      </c>
+      <c r="F8" t="str">
+        <v>THEO_PHONG 3 phòng — chỉ mua TB 2 phòng đầu</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>- Đợt 1: luôn import nhà nguyên căn (HĐ thuê từ chủ). TB bàn giao chỉ ghi nhận, không gắn phòng.</v>
+        <v>HD-WH-RENO-EQUIPONLY</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Không</v>
+      </c>
+      <c r="C9" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Có</v>
+      </c>
+      <c r="F9" t="str">
+        <v>NGUYEN_CAN — không dòng cải tạo, chỉ mua TB</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>- Đợt 2: sheet "1. Cau_Hinh_Khai_Thac" quyết định NGUYEN_CAN hay THEO_PHONG.</v>
+        <v>HD-WH-RENO-MINIMAL</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Có</v>
+      </c>
+      <c r="C10" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Không</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Hà Nội — 1 dòng cải tạo, không mua TB</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>- THEO_PHONG: sheet "2. Danh_Sach_Phong" bắt buộc đủ Số phòng khai thác.</v>
+        <v>HD-WH-NORENO-DAMAGE</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Có</v>
+      </c>
+      <c r="C11" t="str">
+        <v>—</v>
+      </c>
+      <c r="D11" t="str">
+        <v>—</v>
+      </c>
+      <c r="E11" t="str">
+        <v>—</v>
+      </c>
+      <c r="F11" t="str">
+        <v>TB bàn giao DAMAGED/BROKEN/NEW — gửi Host sau đợt 1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>HD-WH-RENO-STRUCT</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Có</v>
+      </c>
+      <c r="C12" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Có</v>
+      </c>
+      <c r="F12" t="str">
+        <v>NGUYEN_CAN — nhiều hạng mục cải tạo STRUCTURAL + mua TB</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Có</v>
+      </c>
+      <c r="C13" t="str">
+        <v>THEO_PHONG (12 phòng)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Có</v>
+      </c>
+      <c r="F13" t="str">
+        <v>THEO_PHONG 12 phòng — dataset lớn nhất</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HD-WH-NORENO-HANOI</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Có</v>
+      </c>
+      <c r="C14" t="str">
+        <v>—</v>
+      </c>
+      <c r="D14" t="str">
+        <v>—</v>
+      </c>
+      <c r="E14" t="str">
+        <v>—</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Hà Nội NORENO — gửi Host sau đợt 1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HD-WH-RENO-HANOI</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Có</v>
+      </c>
+      <c r="C15" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Có</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Hà Nội NGUYEN_CAN — biệt thự cao cấp</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Có</v>
+      </c>
+      <c r="C16" t="str">
+        <v>THEO_PHONG (5 phòng)</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Có</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Hà Nội THEO_PHONG 5 phòng</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Quy tắc:</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>- Đợt 1: luôn import nhà nguyên căn (HĐ thuê từ chủ). TB bàn giao chỉ ghi nhận, không gắn phòng.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>- Đợt 2: sheet "1. Cau_Hinh_Khai_Thac" quyết định NGUYEN_CAN hay THEO_PHONG.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>- THEO_PHONG: sheet "2. Danh_Sach_Phong" bắt buộc đủ Số phòng khai thác.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
         <v>- HD-*-NORENO-*: không có dòng trong file đợt 2.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>- Tổng 15 kịch bản demo (11 có đợt 2).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -889,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C12"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
@@ -940,16 +1145,104 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B5" t="str">
+        <v>THEO_PHONG</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>HD-WH-RENO-SPLIT3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>THEO_PHONG</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>HD-WH-RENO-EQUIPONLY</v>
+      </c>
+      <c r="B7" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HD-WH-RENO-MINIMAL</v>
+      </c>
+      <c r="B8" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HD-WH-RENO-STRUCT</v>
+      </c>
+      <c r="B9" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B10" t="str">
+        <v>THEO_PHONG</v>
+      </c>
+      <c r="C10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HD-WH-RENO-HANOI</v>
+      </c>
+      <c r="B11" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B12" t="str">
+        <v>THEO_PHONG</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E34"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1060,16 +1353,492 @@
         <v>Phòng 105</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B7" t="str">
+        <v>101</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Phòng 101</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B8" t="str">
+        <v>102</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Phòng 102</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>103</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Phòng 103</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B10" t="str">
+        <v>104</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Phòng 104</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>105</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Phòng 105</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B12" t="str">
+        <v>106</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Phòng 106</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B13" t="str">
+        <v>107</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Phòng 107</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B14" t="str">
+        <v>108</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Phòng 108</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HD-WH-RENO-SPLIT3</v>
+      </c>
+      <c r="B15" t="str">
+        <v>101</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>25</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Phòng 101</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HD-WH-RENO-SPLIT3</v>
+      </c>
+      <c r="B16" t="str">
+        <v>102</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>25</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Phòng 102</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HD-WH-RENO-SPLIT3</v>
+      </c>
+      <c r="B17" t="str">
+        <v>103</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>25</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Phòng 103</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B18" t="str">
+        <v>101</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>18.3</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Phòng 101</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B19" t="str">
+        <v>102</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>18.3</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Phòng 102</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B20" t="str">
+        <v>103</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>18.3</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Phòng 103</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B21" t="str">
+        <v>104</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>18.3</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Phòng 104</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B22" t="str">
+        <v>105</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>18.3</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Phòng 105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B23" t="str">
+        <v>106</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>18.3</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Phòng 106</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B24" t="str">
+        <v>107</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>18.3</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Phòng 107</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B25" t="str">
+        <v>108</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>18.3</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Phòng 108</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B26" t="str">
+        <v>109</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>18.3</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Phòng 109</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B27" t="str">
+        <v>110</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>18.3</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Phòng 110</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B28" t="str">
+        <v>111</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>18.3</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Phòng 111</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B29" t="str">
+        <v>112</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>18.3</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Phòng 112</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B30" t="str">
+        <v>101</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>20</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Phòng 101</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B31" t="str">
+        <v>102</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>20</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Phòng 102</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B32" t="str">
+        <v>103</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>20</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Phòng 103</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B33" t="str">
+        <v>104</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>20</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Phòng 104</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B34" t="str">
+        <v>105</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>20</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Phòng 105</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E31"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
@@ -1131,19 +1900,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HD-WH-RENO-NOFURN</v>
+        <v>HD-WH-RENO-FURN</v>
       </c>
       <c r="B4" t="str">
-        <v>FURNITURE</v>
+        <v>FLOORING</v>
       </c>
       <c r="C4" t="str">
-        <v>Nội thất</v>
+        <v>Sàn nhà</v>
       </c>
       <c r="D4">
-        <v>80000000</v>
+        <v>12000000</v>
       </c>
       <c r="E4" t="str">
-        <v>Hoàn thiện nội thất cao cấp</v>
+        <v>Sàn gỗ phòng ngủ</v>
       </c>
     </row>
     <row r="5">
@@ -1151,62 +1920,470 @@
         <v>HD-WH-RENO-NOFURN</v>
       </c>
       <c r="B5" t="str">
-        <v>PLUMBING</v>
+        <v>FURNITURE</v>
       </c>
       <c r="C5" t="str">
-        <v>Điện nước</v>
+        <v>Nội thất</v>
       </c>
       <c r="D5">
-        <v>30000000</v>
+        <v>80000000</v>
       </c>
       <c r="E5" t="str">
-        <v>Smart home</v>
+        <v>Hoàn thiện nội thất cao cấp</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HD-WH-RENO-SPLIT</v>
+        <v>HD-WH-RENO-NOFURN</v>
       </c>
       <c r="B6" t="str">
-        <v>FLOORING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C6" t="str">
-        <v>Sàn nhà</v>
+        <v>Điện nước</v>
       </c>
       <c r="D6">
-        <v>25000000</v>
+        <v>30000000</v>
       </c>
       <c r="E6" t="str">
-        <v>Lát gạch 5 phòng</v>
+        <v>Smart home</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HD-WH-RENO-SPLIT</v>
+        <v>HD-WH-RENO-NOFURN</v>
       </c>
       <c r="B7" t="str">
-        <v>PLUMBING</v>
+        <v>PAINTING</v>
       </c>
       <c r="C7" t="str">
-        <v>Điện nước</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D7">
         <v>15000000</v>
       </c>
       <c r="E7" t="str">
+        <v>Sơn nước cao cấp</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HD-WH-RENO-SPLIT</v>
+      </c>
+      <c r="B8" t="str">
+        <v>FLOORING</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Sàn nhà</v>
+      </c>
+      <c r="D8">
+        <v>25000000</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Lát gạch 5 phòng</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HD-WH-RENO-SPLIT</v>
+      </c>
+      <c r="B9" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D9">
+        <v>15000000</v>
+      </c>
+      <c r="E9" t="str">
         <v>Sửa WC từng phòng</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HD-WH-RENO-SPLIT</v>
+      </c>
+      <c r="B10" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D10">
+        <v>10000000</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Sơn hành lang + phòng</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>STRUCTURAL</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Kết cấu</v>
+      </c>
+      <c r="D11">
+        <v>35000000</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Ngăn vách 8 phòng</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B12" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D12">
+        <v>28000000</v>
+      </c>
+      <c r="E12" t="str">
+        <v>WC riêng từng phòng</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B13" t="str">
+        <v>FLOORING</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Sàn nhà</v>
+      </c>
+      <c r="D13">
+        <v>32000000</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Gạch chống trơn</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B14" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D14">
+        <v>18000000</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Sơn toàn bộ</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HD-WH-RENO-SPLIT3</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D15">
+        <v>8000000</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Sơn 3 phòng</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HD-WH-RENO-SPLIT3</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D16">
+        <v>6500000</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Sửa điện nước</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HD-WH-RENO-MINIMAL</v>
+      </c>
+      <c r="B17" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D17">
+        <v>5500000</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Sơn lại tường tầng 1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HD-WH-RENO-STRUCT</v>
+      </c>
+      <c r="B18" t="str">
+        <v>STRUCTURAL</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Kết cấu</v>
+      </c>
+      <c r="D18">
+        <v>45000000</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Phá vách mở rộng phòng khách</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HD-WH-RENO-STRUCT</v>
+      </c>
+      <c r="B19" t="str">
+        <v>FLOORING</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Sàn nhà</v>
+      </c>
+      <c r="D19">
+        <v>20000000</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Sàn gỗ công nghiệp</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HD-WH-RENO-STRUCT</v>
+      </c>
+      <c r="B20" t="str">
+        <v>FURNITURE</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Nội thất</v>
+      </c>
+      <c r="D20">
+        <v>55000000</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Bộ sofa + bàn ăn mới</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HD-WH-RENO-STRUCT</v>
+      </c>
+      <c r="B21" t="str">
+        <v>OTHER</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Khác</v>
+      </c>
+      <c r="D21">
+        <v>8000000</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Hệ thống đèn LED</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B22" t="str">
+        <v>STRUCTURAL</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Kết cấu</v>
+      </c>
+      <c r="D22">
+        <v>60000000</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Ngăn 12 phòng</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B23" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D23">
+        <v>42000000</v>
+      </c>
+      <c r="E23" t="str">
+        <v>WC chung + riêng</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B24" t="str">
+        <v>FLOORING</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Sàn nhà</v>
+      </c>
+      <c r="D24">
+        <v>38000000</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Gạch 12 phòng</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B25" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D25">
+        <v>22000000</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B26" t="str">
+        <v>EQUIPMENT</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Thiết bị</v>
+      </c>
+      <c r="D26">
+        <v>15000000</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Tủ locker chung</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HD-WH-RENO-HANOI</v>
+      </c>
+      <c r="B27" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D27">
+        <v>25000000</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Sơn ngoại thất + nội thất</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HD-WH-RENO-HANOI</v>
+      </c>
+      <c r="B28" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D28">
+        <v>35000000</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Nâng cấp điện 3 pha</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HD-WH-RENO-HANOI</v>
+      </c>
+      <c r="B29" t="str">
+        <v>FURNITURE</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Nội thất</v>
+      </c>
+      <c r="D29">
+        <v>90000000</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Nội thất full</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B30" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D30">
+        <v>12000000</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B31" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D31">
+        <v>14000000</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Sửa WC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L45"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1338,16 +2515,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HD-WH-RENO-SPLIT</v>
+        <v>HD-WH-RENO-FURN</v>
       </c>
       <c r="B4" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>BATHROOM</v>
       </c>
       <c r="D4" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E4" t="str">
         <v>NEW</v>
@@ -1356,22 +2533,22 @@
         <v>THEM_MOI</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>4200000</v>
+        <v>2800000</v>
       </c>
       <c r="I4">
         <v>12</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K4" t="str">
-        <v>2027-05-28</v>
+        <v>2027-03-31</v>
       </c>
       <c r="L4" t="str">
-        <v>Lắp mới phòng 101</v>
+        <v>Nóng lạnh 2 WC</v>
       </c>
     </row>
     <row r="5">
@@ -1379,13 +2556,13 @@
         <v>HD-WH-RENO-SPLIT</v>
       </c>
       <c r="B5" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E5" t="str">
         <v>NEW</v>
@@ -1397,19 +2574,19 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>8000000</v>
+        <v>4200000</v>
       </c>
       <c r="I5">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K5" t="str">
-        <v>2028-05-28</v>
+        <v>2027-04-28</v>
       </c>
       <c r="L5" t="str">
-        <v>Lắp mới phòng 102</v>
+        <v>Lắp mới phòng 101</v>
       </c>
     </row>
     <row r="6">
@@ -1417,13 +2594,13 @@
         <v>HD-WH-RENO-SPLIT</v>
       </c>
       <c r="B6" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>Tủ quần áo</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E6" t="str">
         <v>NEW</v>
@@ -1435,19 +2612,19 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>3200000</v>
+        <v>8000000</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K6" t="str">
-        <v>2027-05-28</v>
+        <v>2028-04-28</v>
       </c>
       <c r="L6" t="str">
-        <v>Lắp mới phòng 103</v>
+        <v>Lắp mới phòng 102</v>
       </c>
     </row>
     <row r="7">
@@ -1455,13 +2632,13 @@
         <v>HD-WH-RENO-SPLIT</v>
       </c>
       <c r="B7" t="str">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>Nóng lạnh</v>
+        <v>Tủ quần áo</v>
       </c>
       <c r="E7" t="str">
         <v>NEW</v>
@@ -1473,19 +2650,19 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>2500000</v>
+        <v>3200000</v>
       </c>
       <c r="I7">
         <v>12</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K7" t="str">
-        <v>2027-05-28</v>
+        <v>2027-04-28</v>
       </c>
       <c r="L7" t="str">
-        <v>Lắp mới phòng 104</v>
+        <v>Lắp mới phòng 103</v>
       </c>
     </row>
     <row r="8">
@@ -1493,42 +2670,1448 @@
         <v>HD-WH-RENO-SPLIT</v>
       </c>
       <c r="B8" t="str">
+        <v>104</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E8" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F8" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>2500000</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K8" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Lắp mới phòng 104</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HD-WH-RENO-SPLIT</v>
+      </c>
+      <c r="B9" t="str">
         <v>105</v>
       </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
         <v>Quạt</v>
       </c>
-      <c r="E8" t="str">
-        <v>NEW</v>
-      </c>
-      <c r="F8" t="str">
-        <v>THEM_MOI</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
+      <c r="E9" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F9" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
         <v>800000</v>
       </c>
-      <c r="I8">
+      <c r="I9">
         <v>6</v>
       </c>
-      <c r="J8" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="K8" t="str">
-        <v>2026-11-28</v>
-      </c>
-      <c r="L8" t="str">
+      <c r="J9" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Lắp mới phòng 105</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B10" t="str">
+        <v>101</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E10" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F10" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>4200000</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Lắp mới phòng 101</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>102</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E11" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F11" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>8000000</v>
+      </c>
+      <c r="I11">
+        <v>24</v>
+      </c>
+      <c r="J11" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2028-02-28</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Lắp mới phòng 102</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B12" t="str">
+        <v>103</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>Tủ quần áo</v>
+      </c>
+      <c r="E12" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F12" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>3200000</v>
+      </c>
+      <c r="I12">
+        <v>12</v>
+      </c>
+      <c r="J12" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Lắp mới phòng 103</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B13" t="str">
+        <v>104</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E13" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F13" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>2500000</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Lắp mới phòng 104</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B14" t="str">
+        <v>105</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E14" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F14" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>800000</v>
+      </c>
+      <c r="I14">
+        <v>6</v>
+      </c>
+      <c r="J14" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Lắp mới phòng 105</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B15" t="str">
+        <v>106</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>Bàn ăn</v>
+      </c>
+      <c r="E15" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F15" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>2100000</v>
+      </c>
+      <c r="I15">
+        <v>12</v>
+      </c>
+      <c r="J15" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Lắp mới phòng 106</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B16" t="str">
+        <v>107</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E16" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F16" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>4200000</v>
+      </c>
+      <c r="I16">
+        <v>12</v>
+      </c>
+      <c r="J16" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Lắp mới phòng 107</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HD-WH-RENO-SPLIT8</v>
+      </c>
+      <c r="B17" t="str">
+        <v>108</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E17" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F17" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>8000000</v>
+      </c>
+      <c r="I17">
+        <v>24</v>
+      </c>
+      <c r="J17" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2028-02-28</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Lắp mới phòng 108</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HD-WH-RENO-SPLIT3</v>
+      </c>
+      <c r="B18" t="str">
+        <v>101</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E18" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F18" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>4200000</v>
+      </c>
+      <c r="I18">
+        <v>12</v>
+      </c>
+      <c r="J18" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2027-07-28</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Lắp mới phòng 101</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HD-WH-RENO-SPLIT3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>102</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E19" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F19" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>8000000</v>
+      </c>
+      <c r="I19">
+        <v>24</v>
+      </c>
+      <c r="J19" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="K19" t="str">
+        <v>2028-07-28</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Lắp mới phòng 102</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HD-WH-RENO-EQUIPONLY</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E20" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F20" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>12000000</v>
+      </c>
+      <c r="I20">
+        <v>24</v>
+      </c>
+      <c r="J20" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2028-08-31</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HD-WH-RENO-EQUIPONLY</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>KITCHEN</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="E21" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F21" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>8500000</v>
+      </c>
+      <c r="I21">
+        <v>24</v>
+      </c>
+      <c r="J21" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K21" t="str">
+        <v>2028-08-31</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HD-WH-RENO-EQUIPONLY</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>BATHROOM</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="E22" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F22" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>6200000</v>
+      </c>
+      <c r="I22">
+        <v>12</v>
+      </c>
+      <c r="J22" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K22" t="str">
+        <v>2027-08-31</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Máy giặt cửa trước</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HD-WH-RENO-STRUCT</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E23" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F23" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>14000000</v>
+      </c>
+      <c r="I23">
+        <v>36</v>
+      </c>
+      <c r="J23" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K23" t="str">
+        <v>2029-05-31</v>
+      </c>
+      <c r="L23" t="str">
+        <v>2 máy phòng khách</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HD-WH-RENO-STRUCT</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>KITCHEN</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Bếp từ</v>
+      </c>
+      <c r="E24" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F24" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>7200000</v>
+      </c>
+      <c r="I24">
+        <v>24</v>
+      </c>
+      <c r="J24" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K24" t="str">
+        <v>2028-05-31</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HD-WH-RENO-STRUCT</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>GARAGE</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Khác</v>
+      </c>
+      <c r="E25" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F25" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>3000000</v>
+      </c>
+      <c r="I25">
+        <v>12</v>
+      </c>
+      <c r="J25" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K25" t="str">
+        <v>2027-05-31</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Camera an ninh</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B26" t="str">
+        <v>101</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E26" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F26" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>4200000</v>
+      </c>
+      <c r="I26">
+        <v>12</v>
+      </c>
+      <c r="J26" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K26" t="str">
+        <v>2027-01-28</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Lắp mới phòng 101</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B27" t="str">
+        <v>102</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E27" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F27" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>8000000</v>
+      </c>
+      <c r="I27">
+        <v>24</v>
+      </c>
+      <c r="J27" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K27" t="str">
+        <v>2028-01-28</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Lắp mới phòng 102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B28" t="str">
+        <v>103</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>Tủ quần áo</v>
+      </c>
+      <c r="E28" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F28" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>3200000</v>
+      </c>
+      <c r="I28">
+        <v>12</v>
+      </c>
+      <c r="J28" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K28" t="str">
+        <v>2027-01-28</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Lắp mới phòng 103</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B29" t="str">
+        <v>104</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E29" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F29" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>2500000</v>
+      </c>
+      <c r="I29">
+        <v>12</v>
+      </c>
+      <c r="J29" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K29" t="str">
+        <v>2027-01-28</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Lắp mới phòng 104</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B30" t="str">
+        <v>105</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E30" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F30" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>800000</v>
+      </c>
+      <c r="I30">
+        <v>6</v>
+      </c>
+      <c r="J30" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K30" t="str">
+        <v>2026-07-28</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Lắp mới phòng 105</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B31" t="str">
+        <v>106</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>Bàn ăn</v>
+      </c>
+      <c r="E31" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F31" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>2100000</v>
+      </c>
+      <c r="I31">
+        <v>12</v>
+      </c>
+      <c r="J31" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K31" t="str">
+        <v>2027-01-28</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Lắp mới phòng 106</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B32" t="str">
+        <v>107</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E32" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F32" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>4200000</v>
+      </c>
+      <c r="I32">
+        <v>12</v>
+      </c>
+      <c r="J32" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K32" t="str">
+        <v>2027-01-28</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Lắp mới phòng 107</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B33" t="str">
+        <v>108</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E33" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F33" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>8000000</v>
+      </c>
+      <c r="I33">
+        <v>24</v>
+      </c>
+      <c r="J33" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K33" t="str">
+        <v>2028-01-28</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Lắp mới phòng 108</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B34" t="str">
+        <v>109</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v>Tủ quần áo</v>
+      </c>
+      <c r="E34" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F34" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>3200000</v>
+      </c>
+      <c r="I34">
+        <v>12</v>
+      </c>
+      <c r="J34" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K34" t="str">
+        <v>2027-01-28</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Lắp mới phòng 109</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B35" t="str">
+        <v>110</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E35" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F35" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>2500000</v>
+      </c>
+      <c r="I35">
+        <v>12</v>
+      </c>
+      <c r="J35" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K35" t="str">
+        <v>2027-01-28</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Lắp mới phòng 110</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B36" t="str">
+        <v>111</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E36" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F36" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>800000</v>
+      </c>
+      <c r="I36">
+        <v>6</v>
+      </c>
+      <c r="J36" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K36" t="str">
+        <v>2026-07-28</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Lắp mới phòng 111</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>HD-WH-RENO-SPLIT12</v>
+      </c>
+      <c r="B37" t="str">
+        <v>112</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v>Bàn ăn</v>
+      </c>
+      <c r="E37" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F37" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>2100000</v>
+      </c>
+      <c r="I37">
+        <v>12</v>
+      </c>
+      <c r="J37" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K37" t="str">
+        <v>2027-01-28</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Lắp mới phòng 112</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>HD-WH-RENO-HANOI</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E38" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F38" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <v>17000000</v>
+      </c>
+      <c r="I38">
+        <v>36</v>
+      </c>
+      <c r="J38" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="K38" t="str">
+        <v>2029-04-14</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Bổ sung phòng ngủ</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>HD-WH-RENO-HANOI</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v>KITCHEN</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Bếp từ</v>
+      </c>
+      <c r="E39" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F39" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>12000000</v>
+      </c>
+      <c r="I39">
+        <v>36</v>
+      </c>
+      <c r="J39" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="K39" t="str">
+        <v>2029-04-14</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>HD-WH-RENO-HANOI</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v>BALCONY</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E40" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F40" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
+        <v>900000</v>
+      </c>
+      <c r="I40">
+        <v>12</v>
+      </c>
+      <c r="J40" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="K40" t="str">
+        <v>2027-04-14</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B41" t="str">
+        <v>101</v>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E41" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F41" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>4200000</v>
+      </c>
+      <c r="I41">
+        <v>12</v>
+      </c>
+      <c r="J41" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K41" t="str">
+        <v>2027-06-28</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Lắp mới phòng 101</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B42" t="str">
+        <v>102</v>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E42" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F42" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>8000000</v>
+      </c>
+      <c r="I42">
+        <v>24</v>
+      </c>
+      <c r="J42" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K42" t="str">
+        <v>2028-06-28</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Lắp mới phòng 102</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B43" t="str">
+        <v>103</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v>Tủ quần áo</v>
+      </c>
+      <c r="E43" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F43" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>3200000</v>
+      </c>
+      <c r="I43">
+        <v>12</v>
+      </c>
+      <c r="J43" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K43" t="str">
+        <v>2027-06-28</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Lắp mới phòng 103</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B44" t="str">
+        <v>104</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E44" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F44" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>2500000</v>
+      </c>
+      <c r="I44">
+        <v>12</v>
+      </c>
+      <c r="J44" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K44" t="str">
+        <v>2027-06-28</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Lắp mới phòng 104</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B45" t="str">
+        <v>105</v>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E45" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F45" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>800000</v>
+      </c>
+      <c r="I45">
+        <v>6</v>
+      </c>
+      <c r="J45" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K45" t="str">
+        <v>2026-12-28</v>
+      </c>
+      <c r="L45" t="str">
         <v>Lắp mới phòng 105</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend-web/public/templates/SLMS2026_import_dot2_cai_tao.xlsx
+++ b/frontend-web/public/templates/SLMS2026_import_dot2_cai_tao.xlsx
@@ -643,13 +643,13 @@
         <v>NGUYEN_CAN</v>
       </c>
       <c r="D9" t="str">
-        <v>Không</v>
+        <v>Có</v>
       </c>
       <c r="E9" t="str">
         <v>Có</v>
       </c>
       <c r="F9" t="str">
-        <v>NGUYEN_CAN — không dòng cải tạo, chỉ mua TB</v>
+        <v>NGUYEN_CAN — 1 hạng mục cải tạo nhẹ + mua TB</v>
       </c>
     </row>
     <row r="10">
@@ -1242,13 +1242,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:G34"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1265,6 +1267,12 @@
         <v>Diện tích phòng (m²)</v>
       </c>
       <c r="E1" t="str">
+        <v>Chiều dài (m)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Chiều rộng (m)</v>
+      </c>
+      <c r="G1" t="str">
         <v>Ghi chú</v>
       </c>
     </row>
@@ -1281,7 +1289,13 @@
       <c r="D2">
         <v>24</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E2">
+        <v>5.8</v>
+      </c>
+      <c r="F2">
+        <v>4.1</v>
+      </c>
+      <c r="G2" t="str">
         <v>Phòng 101</v>
       </c>
     </row>
@@ -1298,7 +1312,13 @@
       <c r="D3">
         <v>24</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E3">
+        <v>5.8</v>
+      </c>
+      <c r="F3">
+        <v>4.1</v>
+      </c>
+      <c r="G3" t="str">
         <v>Phòng 102</v>
       </c>
     </row>
@@ -1315,7 +1335,13 @@
       <c r="D4">
         <v>24</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4">
+        <v>5.8</v>
+      </c>
+      <c r="F4">
+        <v>4.1</v>
+      </c>
+      <c r="G4" t="str">
         <v>Phòng 103</v>
       </c>
     </row>
@@ -1332,7 +1358,13 @@
       <c r="D5">
         <v>24</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5">
+        <v>5.8</v>
+      </c>
+      <c r="F5">
+        <v>4.1</v>
+      </c>
+      <c r="G5" t="str">
         <v>Phòng 104</v>
       </c>
     </row>
@@ -1349,7 +1381,13 @@
       <c r="D6">
         <v>24</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E6">
+        <v>5.8</v>
+      </c>
+      <c r="F6">
+        <v>4.1</v>
+      </c>
+      <c r="G6" t="str">
         <v>Phòng 105</v>
       </c>
     </row>
@@ -1366,7 +1404,13 @@
       <c r="D7">
         <v>20</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E7">
+        <v>5.3</v>
+      </c>
+      <c r="F7">
+        <v>3.8</v>
+      </c>
+      <c r="G7" t="str">
         <v>Phòng 101</v>
       </c>
     </row>
@@ -1383,7 +1427,13 @@
       <c r="D8">
         <v>20</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E8">
+        <v>5.3</v>
+      </c>
+      <c r="F8">
+        <v>3.8</v>
+      </c>
+      <c r="G8" t="str">
         <v>Phòng 102</v>
       </c>
     </row>
@@ -1400,7 +1450,13 @@
       <c r="D9">
         <v>20</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E9">
+        <v>5.3</v>
+      </c>
+      <c r="F9">
+        <v>3.8</v>
+      </c>
+      <c r="G9" t="str">
         <v>Phòng 103</v>
       </c>
     </row>
@@ -1417,7 +1473,13 @@
       <c r="D10">
         <v>20</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E10">
+        <v>5.3</v>
+      </c>
+      <c r="F10">
+        <v>3.8</v>
+      </c>
+      <c r="G10" t="str">
         <v>Phòng 104</v>
       </c>
     </row>
@@ -1434,7 +1496,13 @@
       <c r="D11">
         <v>20</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E11">
+        <v>5.3</v>
+      </c>
+      <c r="F11">
+        <v>3.8</v>
+      </c>
+      <c r="G11" t="str">
         <v>Phòng 105</v>
       </c>
     </row>
@@ -1451,7 +1519,13 @@
       <c r="D12">
         <v>20</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E12">
+        <v>5.3</v>
+      </c>
+      <c r="F12">
+        <v>3.8</v>
+      </c>
+      <c r="G12" t="str">
         <v>Phòng 106</v>
       </c>
     </row>
@@ -1468,7 +1542,13 @@
       <c r="D13">
         <v>20</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E13">
+        <v>5.3</v>
+      </c>
+      <c r="F13">
+        <v>3.8</v>
+      </c>
+      <c r="G13" t="str">
         <v>Phòng 107</v>
       </c>
     </row>
@@ -1485,7 +1565,13 @@
       <c r="D14">
         <v>20</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E14">
+        <v>5.3</v>
+      </c>
+      <c r="F14">
+        <v>3.8</v>
+      </c>
+      <c r="G14" t="str">
         <v>Phòng 108</v>
       </c>
     </row>
@@ -1502,7 +1588,13 @@
       <c r="D15">
         <v>25</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E15">
+        <v>5.9</v>
+      </c>
+      <c r="F15">
+        <v>4.2</v>
+      </c>
+      <c r="G15" t="str">
         <v>Phòng 101</v>
       </c>
     </row>
@@ -1519,7 +1611,13 @@
       <c r="D16">
         <v>25</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E16">
+        <v>5.9</v>
+      </c>
+      <c r="F16">
+        <v>4.2</v>
+      </c>
+      <c r="G16" t="str">
         <v>Phòng 102</v>
       </c>
     </row>
@@ -1536,7 +1634,13 @@
       <c r="D17">
         <v>25</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E17">
+        <v>5.9</v>
+      </c>
+      <c r="F17">
+        <v>4.2</v>
+      </c>
+      <c r="G17" t="str">
         <v>Phòng 103</v>
       </c>
     </row>
@@ -1553,7 +1657,13 @@
       <c r="D18">
         <v>18.3</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E18">
+        <v>5.1</v>
+      </c>
+      <c r="F18">
+        <v>3.6</v>
+      </c>
+      <c r="G18" t="str">
         <v>Phòng 101</v>
       </c>
     </row>
@@ -1570,7 +1680,13 @@
       <c r="D19">
         <v>18.3</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E19">
+        <v>5.1</v>
+      </c>
+      <c r="F19">
+        <v>3.6</v>
+      </c>
+      <c r="G19" t="str">
         <v>Phòng 102</v>
       </c>
     </row>
@@ -1587,7 +1703,13 @@
       <c r="D20">
         <v>18.3</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E20">
+        <v>5.1</v>
+      </c>
+      <c r="F20">
+        <v>3.6</v>
+      </c>
+      <c r="G20" t="str">
         <v>Phòng 103</v>
       </c>
     </row>
@@ -1604,7 +1726,13 @@
       <c r="D21">
         <v>18.3</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E21">
+        <v>5.1</v>
+      </c>
+      <c r="F21">
+        <v>3.6</v>
+      </c>
+      <c r="G21" t="str">
         <v>Phòng 104</v>
       </c>
     </row>
@@ -1621,7 +1749,13 @@
       <c r="D22">
         <v>18.3</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E22">
+        <v>5.1</v>
+      </c>
+      <c r="F22">
+        <v>3.6</v>
+      </c>
+      <c r="G22" t="str">
         <v>Phòng 105</v>
       </c>
     </row>
@@ -1638,7 +1772,13 @@
       <c r="D23">
         <v>18.3</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E23">
+        <v>5.1</v>
+      </c>
+      <c r="F23">
+        <v>3.6</v>
+      </c>
+      <c r="G23" t="str">
         <v>Phòng 106</v>
       </c>
     </row>
@@ -1655,7 +1795,13 @@
       <c r="D24">
         <v>18.3</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E24">
+        <v>5.1</v>
+      </c>
+      <c r="F24">
+        <v>3.6</v>
+      </c>
+      <c r="G24" t="str">
         <v>Phòng 107</v>
       </c>
     </row>
@@ -1672,7 +1818,13 @@
       <c r="D25">
         <v>18.3</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E25">
+        <v>5.1</v>
+      </c>
+      <c r="F25">
+        <v>3.6</v>
+      </c>
+      <c r="G25" t="str">
         <v>Phòng 108</v>
       </c>
     </row>
@@ -1689,7 +1841,13 @@
       <c r="D26">
         <v>18.3</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E26">
+        <v>5.1</v>
+      </c>
+      <c r="F26">
+        <v>3.6</v>
+      </c>
+      <c r="G26" t="str">
         <v>Phòng 109</v>
       </c>
     </row>
@@ -1706,7 +1864,13 @@
       <c r="D27">
         <v>18.3</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E27">
+        <v>5.1</v>
+      </c>
+      <c r="F27">
+        <v>3.6</v>
+      </c>
+      <c r="G27" t="str">
         <v>Phòng 110</v>
       </c>
     </row>
@@ -1723,7 +1887,13 @@
       <c r="D28">
         <v>18.3</v>
       </c>
-      <c r="E28" t="str">
+      <c r="E28">
+        <v>5.1</v>
+      </c>
+      <c r="F28">
+        <v>3.6</v>
+      </c>
+      <c r="G28" t="str">
         <v>Phòng 111</v>
       </c>
     </row>
@@ -1740,7 +1910,13 @@
       <c r="D29">
         <v>18.3</v>
       </c>
-      <c r="E29" t="str">
+      <c r="E29">
+        <v>5.1</v>
+      </c>
+      <c r="F29">
+        <v>3.6</v>
+      </c>
+      <c r="G29" t="str">
         <v>Phòng 112</v>
       </c>
     </row>
@@ -1757,7 +1933,13 @@
       <c r="D30">
         <v>20</v>
       </c>
-      <c r="E30" t="str">
+      <c r="E30">
+        <v>5.3</v>
+      </c>
+      <c r="F30">
+        <v>3.8</v>
+      </c>
+      <c r="G30" t="str">
         <v>Phòng 101</v>
       </c>
     </row>
@@ -1774,7 +1956,13 @@
       <c r="D31">
         <v>20</v>
       </c>
-      <c r="E31" t="str">
+      <c r="E31">
+        <v>5.3</v>
+      </c>
+      <c r="F31">
+        <v>3.8</v>
+      </c>
+      <c r="G31" t="str">
         <v>Phòng 102</v>
       </c>
     </row>
@@ -1791,7 +1979,13 @@
       <c r="D32">
         <v>20</v>
       </c>
-      <c r="E32" t="str">
+      <c r="E32">
+        <v>5.3</v>
+      </c>
+      <c r="F32">
+        <v>3.8</v>
+      </c>
+      <c r="G32" t="str">
         <v>Phòng 103</v>
       </c>
     </row>
@@ -1808,7 +2002,13 @@
       <c r="D33">
         <v>20</v>
       </c>
-      <c r="E33" t="str">
+      <c r="E33">
+        <v>5.3</v>
+      </c>
+      <c r="F33">
+        <v>3.8</v>
+      </c>
+      <c r="G33" t="str">
         <v>Phòng 104</v>
       </c>
     </row>
@@ -1825,20 +2025,26 @@
       <c r="D34">
         <v>20</v>
       </c>
-      <c r="E34" t="str">
+      <c r="E34">
+        <v>5.3</v>
+      </c>
+      <c r="F34">
+        <v>3.8</v>
+      </c>
+      <c r="G34" t="str">
         <v>Phòng 105</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
@@ -2121,36 +2327,36 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HD-WH-RENO-MINIMAL</v>
+        <v>HD-WH-RENO-EQUIPONLY</v>
       </c>
       <c r="B17" t="str">
-        <v>PAINTING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C17" t="str">
-        <v>Sơn sửa</v>
+        <v>Thiết bị</v>
       </c>
       <c r="D17">
-        <v>5500000</v>
+        <v>2000000</v>
       </c>
       <c r="E17" t="str">
-        <v>Sơn lại tường tầng 1</v>
+        <v>Hoàn thiện lắp đặt trước bàn giao TB mới</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HD-WH-RENO-STRUCT</v>
+        <v>HD-WH-RENO-MINIMAL</v>
       </c>
       <c r="B18" t="str">
-        <v>STRUCTURAL</v>
+        <v>PAINTING</v>
       </c>
       <c r="C18" t="str">
-        <v>Kết cấu</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D18">
-        <v>45000000</v>
+        <v>5500000</v>
       </c>
       <c r="E18" t="str">
-        <v>Phá vách mở rộng phòng khách</v>
+        <v>Sơn lại tường tầng 1</v>
       </c>
     </row>
     <row r="19">
@@ -2158,16 +2364,16 @@
         <v>HD-WH-RENO-STRUCT</v>
       </c>
       <c r="B19" t="str">
-        <v>FLOORING</v>
+        <v>STRUCTURAL</v>
       </c>
       <c r="C19" t="str">
-        <v>Sàn nhà</v>
+        <v>Kết cấu</v>
       </c>
       <c r="D19">
-        <v>20000000</v>
+        <v>45000000</v>
       </c>
       <c r="E19" t="str">
-        <v>Sàn gỗ công nghiệp</v>
+        <v>Phá vách mở rộng phòng khách</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2381,16 @@
         <v>HD-WH-RENO-STRUCT</v>
       </c>
       <c r="B20" t="str">
-        <v>FURNITURE</v>
+        <v>FLOORING</v>
       </c>
       <c r="C20" t="str">
-        <v>Nội thất</v>
+        <v>Sàn nhà</v>
       </c>
       <c r="D20">
-        <v>55000000</v>
+        <v>20000000</v>
       </c>
       <c r="E20" t="str">
-        <v>Bộ sofa + bàn ăn mới</v>
+        <v>Sàn gỗ công nghiệp</v>
       </c>
     </row>
     <row r="21">
@@ -2192,33 +2398,33 @@
         <v>HD-WH-RENO-STRUCT</v>
       </c>
       <c r="B21" t="str">
-        <v>OTHER</v>
+        <v>FURNITURE</v>
       </c>
       <c r="C21" t="str">
-        <v>Khác</v>
+        <v>Nội thất</v>
       </c>
       <c r="D21">
-        <v>8000000</v>
+        <v>55000000</v>
       </c>
       <c r="E21" t="str">
-        <v>Hệ thống đèn LED</v>
+        <v>Bộ sofa + bàn ăn mới</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HD-WH-RENO-SPLIT12</v>
+        <v>HD-WH-RENO-STRUCT</v>
       </c>
       <c r="B22" t="str">
-        <v>STRUCTURAL</v>
+        <v>OTHER</v>
       </c>
       <c r="C22" t="str">
-        <v>Kết cấu</v>
+        <v>Khác</v>
       </c>
       <c r="D22">
-        <v>60000000</v>
+        <v>8000000</v>
       </c>
       <c r="E22" t="str">
-        <v>Ngăn 12 phòng</v>
+        <v>Hệ thống đèn LED</v>
       </c>
     </row>
     <row r="23">
@@ -2226,16 +2432,16 @@
         <v>HD-WH-RENO-SPLIT12</v>
       </c>
       <c r="B23" t="str">
-        <v>PLUMBING</v>
+        <v>STRUCTURAL</v>
       </c>
       <c r="C23" t="str">
-        <v>Điện nước</v>
+        <v>Kết cấu</v>
       </c>
       <c r="D23">
-        <v>42000000</v>
+        <v>60000000</v>
       </c>
       <c r="E23" t="str">
-        <v>WC chung + riêng</v>
+        <v>Ngăn 12 phòng</v>
       </c>
     </row>
     <row r="24">
@@ -2243,16 +2449,16 @@
         <v>HD-WH-RENO-SPLIT12</v>
       </c>
       <c r="B24" t="str">
-        <v>FLOORING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C24" t="str">
-        <v>Sàn nhà</v>
+        <v>Điện nước</v>
       </c>
       <c r="D24">
-        <v>38000000</v>
+        <v>42000000</v>
       </c>
       <c r="E24" t="str">
-        <v>Gạch 12 phòng</v>
+        <v>WC chung + riêng</v>
       </c>
     </row>
     <row r="25">
@@ -2260,16 +2466,16 @@
         <v>HD-WH-RENO-SPLIT12</v>
       </c>
       <c r="B25" t="str">
-        <v>PAINTING</v>
+        <v>FLOORING</v>
       </c>
       <c r="C25" t="str">
-        <v>Sơn sửa</v>
+        <v>Sàn nhà</v>
       </c>
       <c r="D25">
-        <v>22000000</v>
+        <v>38000000</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>Gạch 12 phòng</v>
       </c>
     </row>
     <row r="26">
@@ -2277,33 +2483,33 @@
         <v>HD-WH-RENO-SPLIT12</v>
       </c>
       <c r="B26" t="str">
-        <v>EQUIPMENT</v>
+        <v>PAINTING</v>
       </c>
       <c r="C26" t="str">
-        <v>Thiết bị</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D26">
-        <v>15000000</v>
+        <v>22000000</v>
       </c>
       <c r="E26" t="str">
-        <v>Tủ locker chung</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HD-WH-RENO-HANOI</v>
+        <v>HD-WH-RENO-SPLIT12</v>
       </c>
       <c r="B27" t="str">
-        <v>PAINTING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C27" t="str">
-        <v>Sơn sửa</v>
+        <v>Thiết bị</v>
       </c>
       <c r="D27">
-        <v>25000000</v>
+        <v>15000000</v>
       </c>
       <c r="E27" t="str">
-        <v>Sơn ngoại thất + nội thất</v>
+        <v>Tủ locker chung</v>
       </c>
     </row>
     <row r="28">
@@ -2311,16 +2517,16 @@
         <v>HD-WH-RENO-HANOI</v>
       </c>
       <c r="B28" t="str">
-        <v>PLUMBING</v>
+        <v>PAINTING</v>
       </c>
       <c r="C28" t="str">
-        <v>Điện nước</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D28">
-        <v>35000000</v>
+        <v>25000000</v>
       </c>
       <c r="E28" t="str">
-        <v>Nâng cấp điện 3 pha</v>
+        <v>Sơn ngoại thất + nội thất</v>
       </c>
     </row>
     <row r="29">
@@ -2328,33 +2534,33 @@
         <v>HD-WH-RENO-HANOI</v>
       </c>
       <c r="B29" t="str">
-        <v>FURNITURE</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C29" t="str">
-        <v>Nội thất</v>
+        <v>Điện nước</v>
       </c>
       <c r="D29">
-        <v>90000000</v>
+        <v>35000000</v>
       </c>
       <c r="E29" t="str">
-        <v>Nội thất full</v>
+        <v>Nâng cấp điện 3 pha</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>HD-WH-RENO-SPLIT5-HN</v>
+        <v>HD-WH-RENO-HANOI</v>
       </c>
       <c r="B30" t="str">
-        <v>PAINTING</v>
+        <v>FURNITURE</v>
       </c>
       <c r="C30" t="str">
-        <v>Sơn sửa</v>
+        <v>Nội thất</v>
       </c>
       <c r="D30">
-        <v>12000000</v>
+        <v>90000000</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>Nội thất full</v>
       </c>
     </row>
     <row r="31">
@@ -2362,21 +2568,38 @@
         <v>HD-WH-RENO-SPLIT5-HN</v>
       </c>
       <c r="B31" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D31">
+        <v>12000000</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HD-WH-RENO-SPLIT5-HN</v>
+      </c>
+      <c r="B32" t="str">
         <v>PLUMBING</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C32" t="str">
         <v>Điện nước</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <v>14000000</v>
       </c>
-      <c r="E31" t="str">
+      <c r="E32" t="str">
         <v>Sửa WC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E32"/>
   </ignoredErrors>
 </worksheet>
 </file>
